--- a/outputs/prodejny-import-template/import_Billa2.xlsx
+++ b/outputs/prodejny-import-template/import_Billa2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirihavlicek/meeting-crm/outputs/prodejny-import-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78CCCE34-BAE2-8440-8AE5-85885E58B49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454F35E5-CC72-7542-B8C3-796043F003C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="18720" windowHeight="17240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="436">
   <si>
     <t>Sablona pro import sekce Prodejny</t>
   </si>
@@ -162,9 +162,6 @@
     <t>BILLA</t>
   </si>
   <si>
-    <t>V Olšinách  108</t>
-  </si>
-  <si>
     <t>Vysočanská  20/382</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
     <t xml:space="preserve">K Ďáblicům 1117/1    </t>
   </si>
   <si>
-    <t>Pražská ulice</t>
-  </si>
-  <si>
     <t>Revoluční 1412</t>
   </si>
   <si>
@@ -279,12 +273,6 @@
     <t>Pražská ulice 950</t>
   </si>
   <si>
-    <t xml:space="preserve">Ekonomická. </t>
-  </si>
-  <si>
-    <t>Polaneckého</t>
-  </si>
-  <si>
     <t>Obchodní 329</t>
   </si>
   <si>
@@ -315,9 +303,6 @@
     <t>Podkrušnohorská 1725</t>
   </si>
   <si>
-    <t>Plzeňská  1700/9</t>
-  </si>
-  <si>
     <t>Sokolovská 1959</t>
   </si>
   <si>
@@ -342,9 +327,6 @@
     <t>Žatecká 987</t>
   </si>
   <si>
-    <t>Krčinova  841/9</t>
-  </si>
-  <si>
     <t>Palachova 1404/2</t>
   </si>
   <si>
@@ -357,9 +339,6 @@
     <t>Krkonošská 647</t>
   </si>
   <si>
-    <t>Terezínská  1120</t>
-  </si>
-  <si>
     <t>Husova 1058</t>
   </si>
   <si>
@@ -378,30 +357,6 @@
     <t>Děčínská 3271</t>
   </si>
   <si>
-    <t>Pražská</t>
-  </si>
-  <si>
-    <t>U Bažantnice</t>
-  </si>
-  <si>
-    <t>Havlíčkova</t>
-  </si>
-  <si>
-    <t>Mileny Hážové</t>
-  </si>
-  <si>
-    <t>Sládkova</t>
-  </si>
-  <si>
-    <t>Armádní</t>
-  </si>
-  <si>
-    <t>Příbramská</t>
-  </si>
-  <si>
-    <t>Čsl. Armády</t>
-  </si>
-  <si>
     <t>Fr. Křižíka  505/23</t>
   </si>
   <si>
@@ -480,30 +435,18 @@
     <t>Hradišťská 2690</t>
   </si>
   <si>
-    <t>Zámecká</t>
-  </si>
-  <si>
-    <t>Plzeňská</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plzeňská 1700/9 </t>
   </si>
   <si>
     <t>Strašice 580</t>
   </si>
   <si>
-    <t>Lidická</t>
-  </si>
-  <si>
     <t>Třída 5. května</t>
   </si>
   <si>
     <t>Jihlava</t>
   </si>
   <si>
-    <t>Masarykova   2051</t>
-  </si>
-  <si>
     <t>M. Majerové 296</t>
   </si>
   <si>
@@ -540,9 +483,6 @@
     <t>Náměstí Republiky 1400</t>
   </si>
   <si>
-    <t xml:space="preserve">Na Spravedlnosti </t>
-  </si>
-  <si>
     <t>Hrdinů Odboje 1606</t>
   </si>
   <si>
@@ -585,18 +525,12 @@
     <t>Polepská 979</t>
   </si>
   <si>
-    <t>Stránského  3033/28</t>
-  </si>
-  <si>
     <t>Třída 1.máje  3086/2</t>
   </si>
   <si>
     <t>Pražská  2643/72</t>
   </si>
   <si>
-    <t>Křídlovická  911/34</t>
-  </si>
-  <si>
     <t>Žarošická  4292/30</t>
   </si>
   <si>
@@ -636,9 +570,6 @@
     <t>Náměstí Svornosti 2573/6</t>
   </si>
   <si>
-    <t>Obřanská</t>
-  </si>
-  <si>
     <t>Křenovická 1854</t>
   </si>
   <si>
@@ -699,9 +630,6 @@
     <t>Ruská ulice 1919/7</t>
   </si>
   <si>
-    <t>Staroměstská ulice 3290</t>
-  </si>
-  <si>
     <t>Jeremiášova 486/1</t>
   </si>
   <si>
@@ -747,9 +675,6 @@
     <t>Na Křižanově pile 944</t>
   </si>
   <si>
-    <t>Bílovecká</t>
-  </si>
-  <si>
     <t>Potoční 1299</t>
   </si>
   <si>
@@ -915,129 +840,51 @@
     <t>Radimova 2322/40</t>
   </si>
   <si>
-    <t>Praha - Strašnice</t>
-  </si>
-  <si>
-    <t>Praha - Prosek</t>
-  </si>
-  <si>
     <t>Říčany u Prahy</t>
   </si>
   <si>
-    <t>Praha - Měcholupy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Praha - Modřany </t>
-  </si>
-  <si>
-    <t>Praha - Celnice</t>
-  </si>
-  <si>
     <t>Beroun</t>
   </si>
   <si>
     <t>Hořovice</t>
   </si>
   <si>
-    <t>Praha - Kbely</t>
-  </si>
-  <si>
-    <t>Praha - Fenix</t>
-  </si>
-  <si>
-    <t>Praha - Myšák</t>
-  </si>
-  <si>
-    <t>Praha - Ruzyně II</t>
-  </si>
-  <si>
-    <t>Praha - Hlavní nádraží</t>
-  </si>
-  <si>
-    <t>Praha - Dolní Počernice</t>
-  </si>
-  <si>
-    <t>Praha - OC Krakov</t>
-  </si>
-  <si>
-    <t>Praha - Radotín</t>
-  </si>
-  <si>
     <t>Lety u Dobřichovic</t>
   </si>
   <si>
     <t>Kostelec nad Černými lesy</t>
   </si>
   <si>
-    <t>Praha - Holešovice</t>
-  </si>
-  <si>
-    <t>Praha - Březiněves</t>
-  </si>
-  <si>
     <t>Kamenice</t>
   </si>
   <si>
-    <t>Praha - Quadrio</t>
-  </si>
-  <si>
     <t>Mníšek pod Brdy</t>
   </si>
   <si>
-    <t>Praha - Dolní Chabry</t>
-  </si>
-  <si>
     <t>Jílové u Prahy</t>
   </si>
   <si>
     <t>Šestajovice</t>
   </si>
   <si>
-    <t>Praha - Komořany</t>
-  </si>
-  <si>
-    <t>Praha - Karlín</t>
-  </si>
-  <si>
     <t>Český Brod</t>
   </si>
   <si>
-    <t>Praha - Uhříněves</t>
-  </si>
-  <si>
     <t>Úvaly</t>
   </si>
   <si>
-    <t>Praha - BLOX</t>
-  </si>
-  <si>
-    <t>Praha - Vinoř</t>
-  </si>
-  <si>
-    <t>Praha - Jinonice Mechanika 2</t>
-  </si>
-  <si>
     <t>Vestec</t>
   </si>
   <si>
     <t>Stránčice</t>
   </si>
   <si>
-    <t>Praha - Poděbradská</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jesenice </t>
   </si>
   <si>
     <t>Chýně</t>
   </si>
   <si>
-    <t>Praha - Kunratice</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Kbely - Polaneckého</t>
-  </si>
-  <si>
     <t>Čestlice</t>
   </si>
   <si>
@@ -1056,27 +903,15 @@
     <t>Jablonec nad Nisou</t>
   </si>
   <si>
-    <t>Teplice II</t>
-  </si>
-  <si>
     <t>Varnsdorf</t>
   </si>
   <si>
-    <t>Liberec - Františkov</t>
-  </si>
-  <si>
     <t>Litvínov</t>
   </si>
   <si>
-    <t>Děčín - Korál</t>
-  </si>
-  <si>
     <t>Čelákovice</t>
   </si>
   <si>
-    <t>Kladno - Kročehlavy</t>
-  </si>
-  <si>
     <t>Liberec</t>
   </si>
   <si>
@@ -1089,18 +924,9 @@
     <t>Mladá Boleslav</t>
   </si>
   <si>
-    <t>Ústí nad Labem -  Forum</t>
-  </si>
-  <si>
     <t>Podbořany</t>
   </si>
   <si>
-    <t>Ústí nad Labem - Krásné Březno</t>
-  </si>
-  <si>
-    <t>Liberec - Plaza</t>
-  </si>
-  <si>
     <t>Neratovice</t>
   </si>
   <si>
@@ -1116,15 +942,6 @@
     <t>Jičín</t>
   </si>
   <si>
-    <t>Most II</t>
-  </si>
-  <si>
-    <t>Teplice - OBI</t>
-  </si>
-  <si>
-    <t>Děčín - Pivovar</t>
-  </si>
-  <si>
     <t>Česká Lípa</t>
   </si>
   <si>
@@ -1134,9 +951,6 @@
     <t>Poděbrady</t>
   </si>
   <si>
-    <t>Mladá Boleslav II.</t>
-  </si>
-  <si>
     <t>Zbiroh</t>
   </si>
   <si>
@@ -1152,9 +966,6 @@
     <t>Tábor</t>
   </si>
   <si>
-    <t>Tábor II.</t>
-  </si>
-  <si>
     <t>Strakonice</t>
   </si>
   <si>
@@ -1170,9 +981,6 @@
     <t>Rokycany</t>
   </si>
   <si>
-    <t>Příbram - OC Skalka</t>
-  </si>
-  <si>
     <t>Milevsko</t>
   </si>
   <si>
@@ -1206,24 +1014,9 @@
     <t>Karlovy Vary</t>
   </si>
   <si>
-    <t>Plzeň - Monika</t>
-  </si>
-  <si>
     <t>Týn nad Vltavou</t>
   </si>
   <si>
-    <t>České Budějovice - Bios</t>
-  </si>
-  <si>
-    <t>České Budějovice - Rožnov</t>
-  </si>
-  <si>
-    <t>České Budějovice - Mar. Kas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Písek - Galerie </t>
-  </si>
-  <si>
     <t>Světlá nad Sázavou</t>
   </si>
   <si>
@@ -1242,9 +1035,6 @@
     <t>Stříbro</t>
   </si>
   <si>
-    <t>Jihlava nájemníci</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Havlíčkův Brod</t>
   </si>
   <si>
@@ -1317,9 +1107,6 @@
     <t>Přelouč</t>
   </si>
   <si>
-    <t>Hradec Králové - Aupark</t>
-  </si>
-  <si>
     <t>Hradec Králové</t>
   </si>
   <si>
@@ -1332,18 +1119,6 @@
     <t>Znojmo</t>
   </si>
   <si>
-    <t>Brno - Rondo</t>
-  </si>
-  <si>
-    <t>Brno - Vinohrady</t>
-  </si>
-  <si>
-    <t>Brno - Medlánky</t>
-  </si>
-  <si>
-    <t>Brno - Lesná</t>
-  </si>
-  <si>
     <t>Uherské Hradiště</t>
   </si>
   <si>
@@ -1362,42 +1137,21 @@
     <t>Mikulov</t>
   </si>
   <si>
-    <t>Zlín - Zlaté Jablko</t>
-  </si>
-  <si>
     <t>Moravská Třebová</t>
   </si>
   <si>
     <t>Nové Město na Moravě</t>
   </si>
   <si>
-    <t>Brno - Perla</t>
-  </si>
-  <si>
-    <t>Brno - Maloměřice</t>
-  </si>
-  <si>
     <t>Slavkov u Brna</t>
   </si>
   <si>
-    <t>Brno - Minoritská</t>
-  </si>
-  <si>
-    <t>Brno - Kavkaz</t>
-  </si>
-  <si>
     <t>Kuřim</t>
   </si>
   <si>
-    <t>Zlín - Centro</t>
-  </si>
-  <si>
     <t>Otrokovice</t>
   </si>
   <si>
-    <t>Brno - Hl.nádraží</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bojkovice </t>
   </si>
   <si>
@@ -1452,30 +1206,12 @@
     <t>Rožnov pod Radhoštěm</t>
   </si>
   <si>
-    <t>Ostrava - Dubina</t>
-  </si>
-  <si>
     <t>Zábřeh na Moravě</t>
   </si>
   <si>
     <t>Hlučín</t>
   </si>
   <si>
-    <t>Ostrava - Luna</t>
-  </si>
-  <si>
-    <t>Frýdek Místek - OC Frýda</t>
-  </si>
-  <si>
-    <t>Olomouc - Bělidla</t>
-  </si>
-  <si>
-    <t>Ostrava - Mariánské Hory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Přerov - Galerie </t>
-  </si>
-  <si>
     <t>Valašské Meziříčí</t>
   </si>
   <si>
@@ -1485,154 +1221,127 @@
     <t>Vejprty</t>
   </si>
   <si>
-    <t>Praha - Prosek II.</t>
-  </si>
-  <si>
-    <t>Praha - Petřiny</t>
-  </si>
-  <si>
-    <t>Praha - Šárka</t>
-  </si>
-  <si>
-    <t>Praha - Metro Florenc</t>
-  </si>
-  <si>
-    <t>Praha - Libeňka</t>
-  </si>
-  <si>
-    <t>Praha - Labe</t>
-  </si>
-  <si>
-    <t>Praha - Rozvoj</t>
-  </si>
-  <si>
-    <t>Praha - Argentinská</t>
-  </si>
-  <si>
-    <t>Praha - Novodvorská</t>
-  </si>
-  <si>
-    <t>Praha - Barrandov I.</t>
-  </si>
-  <si>
-    <t>Praha - Stodůlky</t>
-  </si>
-  <si>
-    <t>Praha - Lužiny</t>
-  </si>
-  <si>
-    <t>Praha - DBK</t>
-  </si>
-  <si>
-    <t>Praha - Malešice</t>
-  </si>
-  <si>
-    <t>Praha - Bělehradská</t>
-  </si>
-  <si>
-    <t>Praha - Řepy</t>
-  </si>
-  <si>
-    <t>Praha - Korunní Dvůr</t>
-  </si>
-  <si>
-    <t>Praha - Dědina</t>
-  </si>
-  <si>
-    <t>Praha - Letná</t>
-  </si>
-  <si>
     <t>Ostrava</t>
   </si>
   <si>
-    <t>Zlín II.</t>
-  </si>
-  <si>
-    <t>Sokolov I.</t>
-  </si>
-  <si>
-    <t>Praha - Karlovo náměstí</t>
-  </si>
-  <si>
-    <t>Beroun II.</t>
-  </si>
-  <si>
-    <t>Plzeň - Luna</t>
-  </si>
-  <si>
-    <t>Brno - Líšeň</t>
-  </si>
-  <si>
-    <t>Brno - Rubín</t>
-  </si>
-  <si>
-    <t>Brno - Kounicova</t>
-  </si>
-  <si>
-    <t>Kolín II.</t>
-  </si>
-  <si>
-    <t>Kladno II</t>
-  </si>
-  <si>
-    <t>Plzeň - Papírnická</t>
-  </si>
-  <si>
     <t>Chomutov</t>
   </si>
   <si>
     <t>Příbram</t>
   </si>
   <si>
-    <t>Olomouc III.</t>
-  </si>
-  <si>
-    <t>Zlín I.</t>
-  </si>
-  <si>
-    <t>Brno - Akát</t>
-  </si>
-  <si>
-    <t>České Budějovice - K.I.N</t>
-  </si>
-  <si>
-    <t>Trutnov I.</t>
-  </si>
-  <si>
-    <t>Strakonice II.</t>
-  </si>
-  <si>
-    <t>České Budějovice III.</t>
-  </si>
-  <si>
     <t>Turnov</t>
   </si>
   <si>
     <t>Děčín</t>
   </si>
   <si>
-    <t>Brno - Srbská</t>
-  </si>
-  <si>
     <t>Vrchlabí</t>
   </si>
   <si>
-    <t>Olomouc IV.</t>
-  </si>
-  <si>
-    <t>Praha - Břevnov</t>
-  </si>
-  <si>
-    <t>Praha - Vítkov</t>
-  </si>
-  <si>
-    <t>Brno - Řečkovice</t>
-  </si>
-  <si>
-    <t>Brno - Omega</t>
-  </si>
-  <si>
-    <t>Praha - Markéta</t>
+    <t>V Olšinách 108</t>
+  </si>
+  <si>
+    <t>Ustí nad Labem</t>
+  </si>
+  <si>
+    <t>Most</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Plzeň</t>
+  </si>
+  <si>
+    <t>Písek</t>
+  </si>
+  <si>
+    <t>Havlíčkova 4797/12</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Sokolov</t>
+  </si>
+  <si>
+    <t>Trutnov</t>
+  </si>
+  <si>
+    <t>Praźská 256</t>
+  </si>
+  <si>
+    <t>K Verneráku 1848/40</t>
+  </si>
+  <si>
+    <t>Polaneckého 931/12</t>
+  </si>
+  <si>
+    <t>Pražská 4296</t>
+  </si>
+  <si>
+    <t>U Bažantnice 1506</t>
+  </si>
+  <si>
+    <t>Havlíčkova 1499</t>
+  </si>
+  <si>
+    <t>Mileny Hážové 1544</t>
+  </si>
+  <si>
+    <t>Sládkova 219</t>
+  </si>
+  <si>
+    <t>Armádní 874</t>
+  </si>
+  <si>
+    <t>Příbramská 2120</t>
+  </si>
+  <si>
+    <t>Čsl. Armády 1</t>
+  </si>
+  <si>
+    <t>Terezínská 1120</t>
+  </si>
+  <si>
+    <t>Krčinova 841/9</t>
+  </si>
+  <si>
+    <t>Plzeňská 1700/9</t>
+  </si>
+  <si>
+    <t>Zámecká 1257</t>
+  </si>
+  <si>
+    <t>Plzeňská 897</t>
+  </si>
+  <si>
+    <t>Potoční 1631</t>
+  </si>
+  <si>
+    <t>Masarykova  2051</t>
+  </si>
+  <si>
+    <t>Na Spravedlnosti 2778</t>
+  </si>
+  <si>
+    <t>Pražská 199</t>
+  </si>
+  <si>
+    <t>Stránského 3033/28</t>
+  </si>
+  <si>
+    <t>Křídlovická 911/34</t>
+  </si>
+  <si>
+    <t>Obřanská 1115/1</t>
+  </si>
+  <si>
+    <t>Staroměstská 3290</t>
+  </si>
+  <si>
+    <t>Bílovecká 386</t>
   </si>
 </sst>
 </file>
@@ -1746,7 +1455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1836,21 +1545,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1928,7 +1622,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2249,7 +1943,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -2480,7 +2174,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G253"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2520,10 +2214,10 @@
         <v>101</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>293</v>
+        <v>13</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>42</v>
+        <v>401</v>
       </c>
       <c r="E2" s="1">
         <v>725206101</v>
@@ -2539,10 +2233,10 @@
         <v>103</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>294</v>
+        <v>13</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>725206103</v>
@@ -2556,10 +2250,10 @@
         <v>104</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>725206104</v>
@@ -2573,10 +2267,10 @@
         <v>105</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>725206105</v>
@@ -2590,10 +2284,10 @@
         <v>107</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>297</v>
+        <v>13</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>725206107</v>
@@ -2607,10 +2301,10 @@
         <v>114</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>298</v>
+        <v>13</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7">
         <v>725206114</v>
@@ -2624,10 +2318,10 @@
         <v>115</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8">
         <v>725206115</v>
@@ -2641,10 +2335,10 @@
         <v>117</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9">
         <v>725206117</v>
@@ -2658,10 +2352,10 @@
         <v>118</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>725206118</v>
@@ -2675,10 +2369,10 @@
         <v>119</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>302</v>
+        <v>13</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>725206119</v>
@@ -2692,10 +2386,10 @@
         <v>120</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>303</v>
+        <v>13</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12">
         <v>725206120</v>
@@ -2709,10 +2403,10 @@
         <v>122</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>304</v>
+        <v>13</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>725206122</v>
@@ -2726,10 +2420,10 @@
         <v>123</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>305</v>
+        <v>13</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14">
         <v>725206123</v>
@@ -2743,10 +2437,10 @@
         <v>124</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>306</v>
+        <v>13</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15">
         <v>725206124</v>
@@ -2760,10 +2454,10 @@
         <v>125</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>307</v>
+        <v>13</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16">
         <v>725206125</v>
@@ -2777,10 +2471,10 @@
         <v>126</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>308</v>
+        <v>13</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>725206126</v>
@@ -2794,10 +2488,10 @@
         <v>127</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18">
         <v>725206127</v>
@@ -2811,10 +2505,10 @@
         <v>130</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>725206130</v>
@@ -2828,10 +2522,10 @@
         <v>131</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>311</v>
+        <v>13</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20">
         <v>725206131</v>
@@ -2845,10 +2539,10 @@
         <v>134</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>312</v>
+        <v>13</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>725206134</v>
@@ -2862,10 +2556,10 @@
         <v>139</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22">
         <v>725206139</v>
@@ -2879,10 +2573,10 @@
         <v>145</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>314</v>
+        <v>13</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23">
         <v>725206145</v>
@@ -2896,10 +2590,10 @@
         <v>146</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24">
         <v>725206146</v>
@@ -2913,10 +2607,10 @@
         <v>147</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>316</v>
+        <v>13</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25">
         <v>725206147</v>
@@ -2930,10 +2624,10 @@
         <v>151</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>66</v>
+        <v>411</v>
       </c>
       <c r="E26">
         <v>725206151</v>
@@ -2947,10 +2641,10 @@
         <v>154</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E27">
         <v>725206154</v>
@@ -2964,10 +2658,10 @@
         <v>156</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>319</v>
+        <v>13</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E28">
         <v>725206156</v>
@@ -2981,10 +2675,10 @@
         <v>157</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>320</v>
+        <v>13</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>725206157</v>
@@ -2998,10 +2692,10 @@
         <v>159</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>725206159</v>
@@ -3015,10 +2709,10 @@
         <v>161</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>322</v>
+        <v>13</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E31">
         <v>725206161</v>
@@ -3032,10 +2726,10 @@
         <v>162</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E32">
         <v>725206162</v>
@@ -3049,10 +2743,10 @@
         <v>168</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>324</v>
+        <v>13</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E33">
         <v>725206168</v>
@@ -3066,27 +2760,27 @@
         <v>169</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>325</v>
+        <v>13</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E34">
         <v>725206169</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="30">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="10">
         <v>171</v>
       </c>
-      <c r="C35" s="22" t="s">
-        <v>326</v>
+      <c r="C35" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E35">
         <v>725206171</v>
@@ -3100,10 +2794,10 @@
         <v>172</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E36">
         <v>725206172</v>
@@ -3117,10 +2811,10 @@
         <v>173</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E37">
         <v>725206173</v>
@@ -3134,10 +2828,10 @@
         <v>174</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>329</v>
+        <v>13</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E38">
         <v>725206174</v>
@@ -3151,10 +2845,10 @@
         <v>175</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E39">
         <v>725206175</v>
@@ -3168,10 +2862,10 @@
         <v>181</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E40">
         <v>725206181</v>
@@ -3184,11 +2878,11 @@
       <c r="B41" s="11">
         <v>182</v>
       </c>
-      <c r="C41" s="23" t="s">
-        <v>332</v>
+      <c r="C41" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="E41">
         <v>725206182</v>
@@ -3202,10 +2896,10 @@
         <v>183</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>333</v>
+        <v>13</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="E42">
         <v>725206183</v>
@@ -3219,10 +2913,10 @@
         <v>184</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E43">
         <v>725206184</v>
@@ -3236,10 +2930,10 @@
         <v>185</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E44">
         <v>725206185</v>
@@ -3253,10 +2947,10 @@
         <v>201</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E45">
         <v>725206201</v>
@@ -3270,10 +2964,10 @@
         <v>202</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E46">
         <v>725206202</v>
@@ -3287,10 +2981,10 @@
         <v>205</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E47">
         <v>725206205</v>
@@ -3304,10 +2998,10 @@
         <v>206</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E48">
         <v>725206206</v>
@@ -3321,10 +3015,10 @@
         <v>207</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E49">
         <v>725206207</v>
@@ -3338,10 +3032,10 @@
         <v>209</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>341</v>
+        <v>289</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E50">
         <v>725206209</v>
@@ -3355,13 +3049,13 @@
         <v>210</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>342</v>
+        <v>292</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E51" t="str">
-        <f t="shared" ref="E2:F65" si="0">"725206"&amp;B51</f>
+        <f t="shared" ref="E51:E65" si="0">"725206"&amp;B51</f>
         <v>725206210</v>
       </c>
     </row>
@@ -3373,10 +3067,10 @@
         <v>211</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>343</v>
+        <v>290</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E52" t="str">
         <f t="shared" si="0"/>
@@ -3391,10 +3085,10 @@
         <v>213</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>93</v>
+        <v>424</v>
       </c>
       <c r="E53" t="str">
         <f t="shared" si="0"/>
@@ -3409,10 +3103,10 @@
         <v>214</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="0"/>
@@ -3427,10 +3121,10 @@
         <v>215</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E55" t="str">
         <f t="shared" si="0"/>
@@ -3445,10 +3139,10 @@
         <v>216</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E56" t="str">
         <f t="shared" si="0"/>
@@ -3463,10 +3157,10 @@
         <v>217</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E57" t="str">
         <f t="shared" si="0"/>
@@ -3481,10 +3175,10 @@
         <v>218</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>349</v>
+        <v>294</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E58" t="str">
         <f t="shared" si="0"/>
@@ -3499,10 +3193,10 @@
         <v>219</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E59" t="str">
         <f t="shared" si="0"/>
@@ -3517,10 +3211,10 @@
         <v>220</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>351</v>
+        <v>402</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E60" t="str">
         <f t="shared" si="0"/>
@@ -3535,28 +3229,28 @@
         <v>222</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E61" t="str">
         <f t="shared" si="0"/>
         <v>725206222</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="10">
         <v>223</v>
       </c>
-      <c r="C62" s="22" t="s">
-        <v>353</v>
+      <c r="C62" s="21" t="s">
+        <v>402</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>102</v>
+        <v>423</v>
       </c>
       <c r="E62" t="str">
         <f t="shared" si="0"/>
@@ -3571,10 +3265,10 @@
         <v>224</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E63" t="str">
         <f t="shared" si="0"/>
@@ -3589,10 +3283,10 @@
         <v>226</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>355</v>
+        <v>297</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="0"/>
@@ -3607,10 +3301,10 @@
         <v>228</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>356</v>
+        <v>298</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E65" t="str">
         <f t="shared" si="0"/>
@@ -3625,10 +3319,10 @@
         <v>229</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>357</v>
+        <v>299</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E66" t="str">
         <f t="shared" ref="E66:E129" si="1">"725206"&amp;B66</f>
@@ -3643,10 +3337,10 @@
         <v>230</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>358</v>
+        <v>300</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>107</v>
+        <v>422</v>
       </c>
       <c r="E67" t="str">
         <f t="shared" si="1"/>
@@ -3661,10 +3355,10 @@
         <v>231</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E68" t="str">
         <f t="shared" si="1"/>
@@ -3679,10 +3373,10 @@
         <v>232</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E69" t="str">
         <f t="shared" si="1"/>
@@ -3697,10 +3391,10 @@
         <v>233</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E70" t="str">
         <f t="shared" si="1"/>
@@ -3715,10 +3409,10 @@
         <v>235</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E71" t="str">
         <f t="shared" si="1"/>
@@ -3733,10 +3427,10 @@
         <v>236</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" si="1"/>
@@ -3751,10 +3445,10 @@
         <v>237</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="1"/>
@@ -3769,10 +3463,10 @@
         <v>238</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>114</v>
+        <v>414</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="1"/>
@@ -3787,10 +3481,10 @@
         <v>240</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>365</v>
+        <v>304</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>115</v>
+        <v>415</v>
       </c>
       <c r="E75" t="str">
         <f t="shared" si="1"/>
@@ -3805,10 +3499,10 @@
         <v>241</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>116</v>
+        <v>416</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="1"/>
@@ -3823,10 +3517,10 @@
         <v>242</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>366</v>
+        <v>295</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>117</v>
+        <v>417</v>
       </c>
       <c r="E77" t="str">
         <f t="shared" si="1"/>
@@ -3841,10 +3535,10 @@
         <v>243</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>118</v>
+        <v>418</v>
       </c>
       <c r="E78" t="str">
         <f t="shared" si="1"/>
@@ -3859,10 +3553,10 @@
         <v>261</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>119</v>
+        <v>419</v>
       </c>
       <c r="E79" t="str">
         <f t="shared" si="1"/>
@@ -3877,10 +3571,10 @@
         <v>264</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="E80" t="str">
         <f t="shared" si="1"/>
@@ -3895,10 +3589,10 @@
         <v>267</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>121</v>
+        <v>421</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" si="1"/>
@@ -3913,10 +3607,10 @@
         <v>302</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E82" t="str">
         <f t="shared" si="1"/>
@@ -3931,10 +3625,10 @@
         <v>304</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>372</v>
+        <v>309</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E83" t="str">
         <f t="shared" si="1"/>
@@ -3949,10 +3643,10 @@
         <v>305</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>373</v>
+        <v>310</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E84" t="str">
         <f t="shared" si="1"/>
@@ -3967,17 +3661,17 @@
         <v>306</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>374</v>
+        <v>311</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="1"/>
         <v>725206306</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15">
+    <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
         <v>41</v>
       </c>
@@ -3985,10 +3679,10 @@
         <v>307</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>375</v>
+        <v>312</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="1"/>
@@ -4003,10 +3697,10 @@
         <v>308</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>376</v>
+        <v>313</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="1"/>
@@ -4021,10 +3715,10 @@
         <v>309</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>374</v>
+        <v>311</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E88" t="str">
         <f t="shared" si="1"/>
@@ -4039,10 +3733,10 @@
         <v>310</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>377</v>
+        <v>314</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E89" t="str">
         <f t="shared" si="1"/>
@@ -4057,10 +3751,10 @@
         <v>311</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E90" t="str">
         <f t="shared" si="1"/>
@@ -4075,10 +3769,10 @@
         <v>312</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>379</v>
+        <v>315</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E91" t="str">
         <f t="shared" si="1"/>
@@ -4093,10 +3787,10 @@
         <v>313</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>380</v>
+        <v>316</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E92" t="str">
         <f t="shared" si="1"/>
@@ -4111,10 +3805,10 @@
         <v>314</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>381</v>
+        <v>317</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E93" t="str">
         <f t="shared" si="1"/>
@@ -4129,10 +3823,10 @@
         <v>315</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>382</v>
+        <v>318</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E94" t="str">
         <f t="shared" si="1"/>
@@ -4147,10 +3841,10 @@
         <v>316</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E95" t="str">
         <f t="shared" si="1"/>
@@ -4165,10 +3859,10 @@
         <v>317</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="1"/>
@@ -4183,10 +3877,10 @@
         <v>318</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>385</v>
+        <v>321</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" si="1"/>
@@ -4201,10 +3895,10 @@
         <v>319</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E98" t="str">
         <f t="shared" si="1"/>
@@ -4219,10 +3913,10 @@
         <v>320</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>387</v>
+        <v>323</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E99" t="str">
         <f t="shared" si="1"/>
@@ -4237,10 +3931,10 @@
         <v>321</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E100" t="str">
         <f t="shared" si="1"/>
@@ -4255,10 +3949,10 @@
         <v>322</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>389</v>
+        <v>325</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E101" t="str">
         <f t="shared" si="1"/>
@@ -4273,10 +3967,10 @@
         <v>324</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E102" t="str">
         <f t="shared" si="1"/>
@@ -4291,10 +3985,10 @@
         <v>325</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>391</v>
+        <v>326</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E103" t="str">
         <f t="shared" si="1"/>
@@ -4309,17 +4003,17 @@
         <v>328</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="E104" t="str">
         <f t="shared" si="1"/>
         <v>725206328</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="30">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -4327,17 +4021,17 @@
         <v>335</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>393</v>
+        <v>311</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E105" t="str">
         <f t="shared" si="1"/>
         <v>725206335</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5">
       <c r="A106" s="1" t="s">
         <v>41</v>
       </c>
@@ -4345,10 +4039,10 @@
         <v>336</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>394</v>
+        <v>311</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E106" t="str">
         <f t="shared" si="1"/>
@@ -4363,10 +4057,10 @@
         <v>338</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E107" t="str">
         <f t="shared" si="1"/>
@@ -4381,10 +4075,10 @@
         <v>339</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>148</v>
+        <v>425</v>
       </c>
       <c r="E108" t="str">
         <f t="shared" si="1"/>
@@ -4399,10 +4093,10 @@
         <v>340</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>149</v>
+        <v>426</v>
       </c>
       <c r="E109" t="str">
         <f t="shared" si="1"/>
@@ -4417,10 +4111,10 @@
         <v>342</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E110" t="str">
         <f t="shared" si="1"/>
@@ -4435,10 +4129,10 @@
         <v>343</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>399</v>
+        <v>330</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E111" t="str">
         <f t="shared" si="1"/>
@@ -4453,10 +4147,10 @@
         <v>345</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>400</v>
+        <v>331</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>152</v>
+        <v>427</v>
       </c>
       <c r="E112" t="str">
         <f t="shared" si="1"/>
@@ -4471,10 +4165,10 @@
         <v>378</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="E113" t="str">
         <f t="shared" si="1"/>
@@ -4489,10 +4183,10 @@
         <v>402</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>402</v>
+        <v>136</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>154</v>
+        <v>407</v>
       </c>
       <c r="E114" t="str">
         <f t="shared" si="1"/>
@@ -4507,10 +4201,10 @@
         <v>403</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>155</v>
+        <v>428</v>
       </c>
       <c r="E115" t="str">
         <f t="shared" si="1"/>
@@ -4525,10 +4219,10 @@
         <v>404</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E116" t="str">
         <f t="shared" si="1"/>
@@ -4543,10 +4237,10 @@
         <v>405</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E117" t="str">
         <f t="shared" si="1"/>
@@ -4561,10 +4255,10 @@
         <v>406</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>406</v>
+        <v>336</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="E118" t="str">
         <f t="shared" si="1"/>
@@ -4579,10 +4273,10 @@
         <v>407</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>407</v>
+        <v>337</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E119" t="str">
         <f t="shared" si="1"/>
@@ -4597,10 +4291,10 @@
         <v>408</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E120" t="str">
         <f t="shared" si="1"/>
@@ -4615,10 +4309,10 @@
         <v>409</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>409</v>
+        <v>339</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E121" t="str">
         <f t="shared" si="1"/>
@@ -4633,10 +4327,10 @@
         <v>411</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="E122" t="str">
         <f t="shared" si="1"/>
@@ -4651,10 +4345,10 @@
         <v>414</v>
       </c>
       <c r="C123" s="23" t="s">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="E123" t="str">
         <f t="shared" si="1"/>
@@ -4669,10 +4363,10 @@
         <v>501</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>412</v>
+        <v>342</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E124" t="str">
         <f t="shared" si="1"/>
@@ -4687,10 +4381,10 @@
         <v>502</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>413</v>
+        <v>343</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E125" t="str">
         <f t="shared" si="1"/>
@@ -4705,10 +4399,10 @@
         <v>503</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>414</v>
+        <v>344</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="E126" t="str">
         <f t="shared" si="1"/>
@@ -4723,10 +4417,10 @@
         <v>504</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="E127" t="str">
         <f t="shared" si="1"/>
@@ -4741,10 +4435,10 @@
         <v>505</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>168</v>
+        <v>429</v>
       </c>
       <c r="E128" t="str">
         <f t="shared" si="1"/>
@@ -4759,10 +4453,10 @@
         <v>506</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>416</v>
+        <v>346</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E129" t="str">
         <f t="shared" si="1"/>
@@ -4777,10 +4471,10 @@
         <v>507</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>417</v>
+        <v>347</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E130" t="str">
         <f t="shared" ref="E130:E193" si="2">"725206"&amp;B130</f>
@@ -4795,10 +4489,10 @@
         <v>508</v>
       </c>
       <c r="C131" s="21" t="s">
-        <v>418</v>
+        <v>348</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E131" t="str">
         <f t="shared" si="2"/>
@@ -4813,10 +4507,10 @@
         <v>509</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>419</v>
+        <v>349</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E132" t="str">
         <f t="shared" si="2"/>
@@ -4831,10 +4525,10 @@
         <v>510</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E133" t="str">
         <f t="shared" si="2"/>
@@ -4849,10 +4543,10 @@
         <v>512</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="E134" t="str">
         <f t="shared" si="2"/>
@@ -4867,10 +4561,10 @@
         <v>514</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E135" t="str">
         <f t="shared" si="2"/>
@@ -4885,10 +4579,10 @@
         <v>515</v>
       </c>
       <c r="C136" s="21" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E136" t="str">
         <f t="shared" si="2"/>
@@ -4903,10 +4597,10 @@
         <v>516</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E137" t="str">
         <f t="shared" si="2"/>
@@ -4921,10 +4615,10 @@
         <v>517</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>425</v>
+        <v>355</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E138" t="str">
         <f t="shared" si="2"/>
@@ -4939,10 +4633,10 @@
         <v>518</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>426</v>
+        <v>356</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E139" t="str">
         <f t="shared" si="2"/>
@@ -4957,10 +4651,10 @@
         <v>519</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>427</v>
+        <v>357</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="E140" t="str">
         <f t="shared" si="2"/>
@@ -4975,10 +4669,10 @@
         <v>520</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>428</v>
+        <v>357</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="E141" t="str">
         <f t="shared" si="2"/>
@@ -4993,10 +4687,10 @@
         <v>521</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>412</v>
+        <v>342</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E142" t="str">
         <f t="shared" si="2"/>
@@ -5011,10 +4705,10 @@
         <v>523</v>
       </c>
       <c r="C143" s="21" t="s">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>114</v>
+        <v>430</v>
       </c>
       <c r="E143" t="str">
         <f t="shared" si="2"/>
@@ -5029,10 +4723,10 @@
         <v>601</v>
       </c>
       <c r="C144" s="21" t="s">
-        <v>429</v>
+        <v>358</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>183</v>
+        <v>431</v>
       </c>
       <c r="E144" t="str">
         <f t="shared" si="2"/>
@@ -5047,10 +4741,10 @@
         <v>603</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="E145" t="str">
         <f t="shared" si="2"/>
@@ -5065,10 +4759,10 @@
         <v>604</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>431</v>
+        <v>360</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E146" t="str">
         <f t="shared" si="2"/>
@@ -5083,10 +4777,10 @@
         <v>605</v>
       </c>
       <c r="C147" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="D147" s="16" t="s">
         <v>432</v>
-      </c>
-      <c r="D147" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="E147" t="str">
         <f t="shared" si="2"/>
@@ -5101,10 +4795,10 @@
         <v>606</v>
       </c>
       <c r="C148" s="21" t="s">
-        <v>433</v>
+        <v>358</v>
       </c>
       <c r="D148" s="16" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="E148" t="str">
         <f t="shared" si="2"/>
@@ -5119,10 +4813,10 @@
         <v>608</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>434</v>
+        <v>358</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="E149" t="str">
         <f t="shared" si="2"/>
@@ -5137,10 +4831,10 @@
         <v>610</v>
       </c>
       <c r="C150" s="21" t="s">
-        <v>435</v>
+        <v>358</v>
       </c>
       <c r="D150" s="16" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="E150" t="str">
         <f t="shared" si="2"/>
@@ -5155,10 +4849,10 @@
         <v>614</v>
       </c>
       <c r="C151" s="21" t="s">
-        <v>436</v>
+        <v>361</v>
       </c>
       <c r="D151" s="16" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="E151" t="str">
         <f t="shared" si="2"/>
@@ -5173,10 +4867,10 @@
         <v>615</v>
       </c>
       <c r="C152" s="21" t="s">
-        <v>437</v>
+        <v>362</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="E152" t="str">
         <f t="shared" si="2"/>
@@ -5191,10 +4885,10 @@
         <v>616</v>
       </c>
       <c r="C153" s="21" t="s">
-        <v>438</v>
+        <v>363</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="E153" t="str">
         <f t="shared" si="2"/>
@@ -5209,10 +4903,10 @@
         <v>617</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>439</v>
+        <v>364</v>
       </c>
       <c r="D154" s="16" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E154" t="str">
         <f t="shared" si="2"/>
@@ -5227,10 +4921,10 @@
         <v>618</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>440</v>
+        <v>365</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E155" t="str">
         <f t="shared" si="2"/>
@@ -5245,10 +4939,10 @@
         <v>620</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>441</v>
+        <v>366</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E156" t="str">
         <f t="shared" si="2"/>
@@ -5263,10 +4957,10 @@
         <v>621</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="E157" t="str">
         <f t="shared" si="2"/>
@@ -5281,10 +4975,10 @@
         <v>624</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>443</v>
+        <v>367</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="E158" t="str">
         <f t="shared" si="2"/>
@@ -5299,10 +4993,10 @@
         <v>625</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>444</v>
+        <v>368</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E159" t="str">
         <f t="shared" si="2"/>
@@ -5316,11 +5010,11 @@
       <c r="B160" s="10">
         <v>627</v>
       </c>
-      <c r="C160" s="21" t="s">
-        <v>445</v>
+      <c r="C160" s="24" t="s">
+        <v>358</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="E160" t="str">
         <f t="shared" si="2"/>
@@ -5334,11 +5028,11 @@
       <c r="B161" s="10">
         <v>628</v>
       </c>
-      <c r="C161" s="21" t="s">
-        <v>446</v>
+      <c r="C161" s="24" t="s">
+        <v>358</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>200</v>
+        <v>433</v>
       </c>
       <c r="E161" t="str">
         <f t="shared" si="2"/>
@@ -5353,10 +5047,10 @@
         <v>629</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>447</v>
+        <v>369</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="E162" t="str">
         <f t="shared" si="2"/>
@@ -5370,11 +5064,11 @@
       <c r="B163" s="10">
         <v>630</v>
       </c>
-      <c r="C163" s="21" t="s">
-        <v>448</v>
+      <c r="C163" s="24" t="s">
+        <v>358</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="E163" t="str">
         <f t="shared" si="2"/>
@@ -5388,11 +5082,11 @@
       <c r="B164" s="10">
         <v>635</v>
       </c>
-      <c r="C164" s="21" t="s">
-        <v>449</v>
+      <c r="C164" s="24" t="s">
+        <v>358</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E164" t="str">
         <f t="shared" si="2"/>
@@ -5407,10 +5101,10 @@
         <v>638</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="D165" s="16" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="E165" t="str">
         <f t="shared" si="2"/>
@@ -5425,10 +5119,10 @@
         <v>640</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>451</v>
+        <v>408</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="E166" t="str">
         <f t="shared" si="2"/>
@@ -5443,10 +5137,10 @@
         <v>643</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="E167" t="str">
         <f t="shared" si="2"/>
@@ -5461,10 +5155,10 @@
         <v>644</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>431</v>
+        <v>360</v>
       </c>
       <c r="D168" s="16" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="E168" t="str">
         <f t="shared" si="2"/>
@@ -5479,10 +5173,10 @@
         <v>647</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>453</v>
+        <v>358</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="E169" t="str">
         <f t="shared" si="2"/>
@@ -5497,10 +5191,10 @@
         <v>649</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>454</v>
+        <v>372</v>
       </c>
       <c r="D170" s="16" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="E170" t="str">
         <f t="shared" si="2"/>
@@ -5515,10 +5209,10 @@
         <v>701</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>455</v>
+        <v>373</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="E171" t="str">
         <f t="shared" si="2"/>
@@ -5533,10 +5227,10 @@
         <v>703</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>456</v>
+        <v>374</v>
       </c>
       <c r="D172" s="16" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="E172" t="str">
         <f t="shared" si="2"/>
@@ -5551,10 +5245,10 @@
         <v>704</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>457</v>
+        <v>375</v>
       </c>
       <c r="D173" s="16" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E173" t="str">
         <f t="shared" si="2"/>
@@ -5569,10 +5263,10 @@
         <v>705</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>458</v>
+        <v>376</v>
       </c>
       <c r="D174" s="16" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="E174" t="str">
         <f t="shared" si="2"/>
@@ -5587,10 +5281,10 @@
         <v>707</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>459</v>
+        <v>377</v>
       </c>
       <c r="D175" s="16" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="E175" t="str">
         <f t="shared" si="2"/>
@@ -5605,10 +5299,10 @@
         <v>708</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>460</v>
+        <v>378</v>
       </c>
       <c r="D176" s="16" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="E176" t="str">
         <f t="shared" si="2"/>
@@ -5623,10 +5317,10 @@
         <v>709</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>461</v>
+        <v>379</v>
       </c>
       <c r="D177" s="16" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="E177" t="str">
         <f t="shared" si="2"/>
@@ -5641,10 +5335,10 @@
         <v>710</v>
       </c>
       <c r="C178" s="21" t="s">
-        <v>462</v>
+        <v>380</v>
       </c>
       <c r="D178" s="16" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="E178" t="str">
         <f t="shared" si="2"/>
@@ -5659,10 +5353,10 @@
         <v>711</v>
       </c>
       <c r="C179" s="21" t="s">
-        <v>463</v>
+        <v>381</v>
       </c>
       <c r="D179" s="16" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="E179" t="str">
         <f t="shared" si="2"/>
@@ -5677,10 +5371,10 @@
         <v>713</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>464</v>
+        <v>382</v>
       </c>
       <c r="D180" s="16" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="E180" t="str">
         <f t="shared" si="2"/>
@@ -5695,10 +5389,10 @@
         <v>714</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>465</v>
+        <v>383</v>
       </c>
       <c r="D181" s="16" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="E181" t="str">
         <f t="shared" si="2"/>
@@ -5713,10 +5407,10 @@
         <v>715</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>466</v>
+        <v>384</v>
       </c>
       <c r="D182" s="16" t="s">
-        <v>221</v>
+        <v>434</v>
       </c>
       <c r="E182" t="str">
         <f t="shared" si="2"/>
@@ -5731,10 +5425,10 @@
         <v>716</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>460</v>
+        <v>378</v>
       </c>
       <c r="D183" s="16" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="E183" t="str">
         <f t="shared" si="2"/>
@@ -5749,10 +5443,10 @@
         <v>717</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>467</v>
+        <v>385</v>
       </c>
       <c r="D184" s="16" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="E184" t="str">
         <f t="shared" si="2"/>
@@ -5767,10 +5461,10 @@
         <v>718</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>468</v>
+        <v>386</v>
       </c>
       <c r="D185" s="16" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E185" t="str">
         <f t="shared" si="2"/>
@@ -5785,10 +5479,10 @@
         <v>721</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>469</v>
+        <v>387</v>
       </c>
       <c r="D186" s="16" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E186" t="str">
         <f t="shared" si="2"/>
@@ -5803,10 +5497,10 @@
         <v>722</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>470</v>
+        <v>388</v>
       </c>
       <c r="D187" s="16" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="E187" t="str">
         <f t="shared" si="2"/>
@@ -5821,10 +5515,10 @@
         <v>723</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>471</v>
+        <v>389</v>
       </c>
       <c r="D188" s="16" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="E188" t="str">
         <f t="shared" si="2"/>
@@ -5839,10 +5533,10 @@
         <v>724</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>472</v>
+        <v>395</v>
       </c>
       <c r="D189" s="16" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="E189" t="str">
         <f t="shared" si="2"/>
@@ -5857,10 +5551,10 @@
         <v>726</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>473</v>
+        <v>390</v>
       </c>
       <c r="D190" s="16" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="E190" t="str">
         <f t="shared" si="2"/>
@@ -5875,10 +5569,10 @@
         <v>728</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="D191" s="16" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="E191" t="str">
         <f t="shared" si="2"/>
@@ -5893,10 +5587,10 @@
         <v>729</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>475</v>
+        <v>395</v>
       </c>
       <c r="D192" s="16" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="E192" t="str">
         <f t="shared" si="2"/>
@@ -5911,10 +5605,10 @@
         <v>731</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>476</v>
+        <v>384</v>
       </c>
       <c r="D193" s="16" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="E193" t="str">
         <f t="shared" si="2"/>
@@ -5929,10 +5623,10 @@
         <v>732</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>477</v>
+        <v>378</v>
       </c>
       <c r="D194" s="16" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="E194" t="str">
         <f t="shared" ref="E194:E253" si="3">"725206"&amp;B194</f>
@@ -5947,10 +5641,10 @@
         <v>733</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>478</v>
+        <v>395</v>
       </c>
       <c r="D195" s="16" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="E195" t="str">
         <f t="shared" si="3"/>
@@ -5965,10 +5659,10 @@
         <v>734</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>479</v>
+        <v>380</v>
       </c>
       <c r="D196" s="16" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="E196" t="str">
         <f t="shared" si="3"/>
@@ -5983,10 +5677,10 @@
         <v>736</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>480</v>
+        <v>392</v>
       </c>
       <c r="D197" s="16" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="E197" t="str">
         <f t="shared" si="3"/>
@@ -6001,10 +5695,10 @@
         <v>741</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>481</v>
+        <v>393</v>
       </c>
       <c r="D198" s="16" t="s">
-        <v>237</v>
+        <v>435</v>
       </c>
       <c r="E198" t="str">
         <f t="shared" si="3"/>
@@ -6019,10 +5713,10 @@
         <v>802</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>482</v>
+        <v>394</v>
       </c>
       <c r="D199" s="16" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="E199" t="str">
         <f t="shared" si="3"/>
@@ -6037,10 +5731,10 @@
         <v>803</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>483</v>
+        <v>13</v>
       </c>
       <c r="D200" s="16" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="E200" t="str">
         <f t="shared" si="3"/>
@@ -6055,10 +5749,10 @@
         <v>804</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>484</v>
+        <v>13</v>
       </c>
       <c r="D201" s="16" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="E201" t="str">
         <f t="shared" si="3"/>
@@ -6073,10 +5767,10 @@
         <v>805</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>485</v>
+        <v>13</v>
       </c>
       <c r="D202" s="16" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="E202" t="str">
         <f t="shared" si="3"/>
@@ -6091,10 +5785,10 @@
         <v>806</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>486</v>
+        <v>13</v>
       </c>
       <c r="D203" s="16" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="E203" t="str">
         <f t="shared" si="3"/>
@@ -6109,10 +5803,10 @@
         <v>807</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>487</v>
+        <v>13</v>
       </c>
       <c r="D204" s="16" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="E204" t="str">
         <f t="shared" si="3"/>
@@ -6127,10 +5821,10 @@
         <v>808</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>488</v>
+        <v>13</v>
       </c>
       <c r="D205" s="16" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="E205" t="str">
         <f t="shared" si="3"/>
@@ -6145,10 +5839,10 @@
         <v>809</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>489</v>
+        <v>13</v>
       </c>
       <c r="D206" s="16" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="E206" t="str">
         <f t="shared" si="3"/>
@@ -6163,10 +5857,10 @@
         <v>810</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>490</v>
+        <v>13</v>
       </c>
       <c r="D207" s="16" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E207" t="str">
         <f t="shared" si="3"/>
@@ -6181,10 +5875,10 @@
         <v>811</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>491</v>
+        <v>13</v>
       </c>
       <c r="D208" s="16" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="E208" t="str">
         <f t="shared" si="3"/>
@@ -6199,10 +5893,10 @@
         <v>812</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>492</v>
+        <v>13</v>
       </c>
       <c r="D209" s="16" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="E209" t="str">
         <f t="shared" si="3"/>
@@ -6217,10 +5911,10 @@
         <v>813</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>493</v>
+        <v>13</v>
       </c>
       <c r="D210" s="16" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="E210" t="str">
         <f t="shared" si="3"/>
@@ -6235,10 +5929,10 @@
         <v>815</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>494</v>
+        <v>13</v>
       </c>
       <c r="D211" s="16" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E211" t="str">
         <f t="shared" si="3"/>
@@ -6253,10 +5947,10 @@
         <v>816</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="D212" s="16" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="E212" t="str">
         <f t="shared" si="3"/>
@@ -6271,10 +5965,10 @@
         <v>818</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>496</v>
+        <v>13</v>
       </c>
       <c r="D213" s="16" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="E213" t="str">
         <f t="shared" si="3"/>
@@ -6289,10 +5983,10 @@
         <v>819</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>497</v>
+        <v>13</v>
       </c>
       <c r="D214" s="16" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="E214" t="str">
         <f t="shared" si="3"/>
@@ -6307,10 +6001,10 @@
         <v>822</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>498</v>
+        <v>13</v>
       </c>
       <c r="D215" s="16" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="E215" t="str">
         <f t="shared" si="3"/>
@@ -6325,10 +6019,10 @@
         <v>823</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>499</v>
+        <v>13</v>
       </c>
       <c r="D216" s="16" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="E216" t="str">
         <f t="shared" si="3"/>
@@ -6343,10 +6037,10 @@
         <v>825</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="D217" s="16" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="E217" t="str">
         <f t="shared" si="3"/>
@@ -6361,10 +6055,10 @@
         <v>826</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="D218" s="16" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="E218" t="str">
         <f t="shared" si="3"/>
@@ -6379,10 +6073,10 @@
         <v>827</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>502</v>
+        <v>395</v>
       </c>
       <c r="D219" s="16" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="E219" t="str">
         <f t="shared" si="3"/>
@@ -6397,10 +6091,10 @@
         <v>828</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="D220" s="16" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="E220" t="str">
         <f t="shared" si="3"/>
@@ -6415,10 +6109,10 @@
         <v>831</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>504</v>
+        <v>409</v>
       </c>
       <c r="D221" s="16" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="E221" t="str">
         <f t="shared" si="3"/>
@@ -6433,10 +6127,10 @@
         <v>832</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>505</v>
+        <v>13</v>
       </c>
       <c r="D222" s="16" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="E222" t="str">
         <f t="shared" si="3"/>
@@ -6451,10 +6145,10 @@
         <v>833</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>506</v>
+        <v>269</v>
       </c>
       <c r="D223" s="16" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="E223" t="str">
         <f t="shared" si="3"/>
@@ -6469,10 +6163,10 @@
         <v>834</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>507</v>
+        <v>405</v>
       </c>
       <c r="D224" s="16" t="s">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="E224" t="str">
         <f t="shared" si="3"/>
@@ -6487,10 +6181,10 @@
         <v>835</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>508</v>
+        <v>358</v>
       </c>
       <c r="D225" s="16" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="E225" t="str">
         <f t="shared" si="3"/>
@@ -6505,10 +6199,10 @@
         <v>836</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="D226" s="16" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="E226" t="str">
         <f t="shared" si="3"/>
@@ -6523,10 +6217,10 @@
         <v>838</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>510</v>
+        <v>358</v>
       </c>
       <c r="D227" s="16" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="E227" t="str">
         <f t="shared" si="3"/>
@@ -6541,10 +6235,10 @@
         <v>839</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>511</v>
+        <v>342</v>
       </c>
       <c r="D228" s="16" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="E228" t="str">
         <f t="shared" si="3"/>
@@ -6559,10 +6253,10 @@
         <v>840</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>512</v>
+        <v>285</v>
       </c>
       <c r="D229" s="16" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="E229" t="str">
         <f t="shared" si="3"/>
@@ -6577,10 +6271,10 @@
         <v>844</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D230" s="16" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="E230" t="str">
         <f t="shared" si="3"/>
@@ -6595,10 +6289,10 @@
         <v>845</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>513</v>
+        <v>405</v>
       </c>
       <c r="D231" s="16" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="E231" t="str">
         <f t="shared" si="3"/>
@@ -6613,10 +6307,10 @@
         <v>846</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="D232" s="16" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="E232" t="str">
         <f t="shared" si="3"/>
@@ -6631,10 +6325,10 @@
         <v>847</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>514</v>
+        <v>396</v>
       </c>
       <c r="D233" s="16" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="E233" t="str">
         <f t="shared" si="3"/>
@@ -6649,10 +6343,10 @@
         <v>848</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>515</v>
+        <v>397</v>
       </c>
       <c r="D234" s="16" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="E234" t="str">
         <f t="shared" si="3"/>
@@ -6667,10 +6361,10 @@
         <v>849</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>516</v>
+        <v>378</v>
       </c>
       <c r="D235" s="16" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="E235" t="str">
         <f t="shared" si="3"/>
@@ -6685,10 +6379,10 @@
         <v>853</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>517</v>
+        <v>408</v>
       </c>
       <c r="D236" s="16" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="E236" t="str">
         <f t="shared" si="3"/>
@@ -6703,10 +6397,10 @@
         <v>856</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>518</v>
+        <v>358</v>
       </c>
       <c r="D237" s="16" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="E237" t="str">
         <f t="shared" si="3"/>
@@ -6721,10 +6415,10 @@
         <v>857</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>519</v>
+        <v>311</v>
       </c>
       <c r="D238" s="16" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="E238" t="str">
         <f t="shared" si="3"/>
@@ -6739,10 +6433,10 @@
         <v>858</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>520</v>
+        <v>410</v>
       </c>
       <c r="D239" s="16" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="E239" t="str">
         <f t="shared" si="3"/>
@@ -6757,10 +6451,10 @@
         <v>859</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>521</v>
+        <v>310</v>
       </c>
       <c r="D240" s="16" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="E240" t="str">
         <f t="shared" si="3"/>
@@ -6775,10 +6469,10 @@
         <v>869</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>522</v>
+        <v>311</v>
       </c>
       <c r="D241" s="16" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E241" t="str">
         <f t="shared" si="3"/>
@@ -6793,10 +6487,10 @@
         <v>874</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>523</v>
+        <v>398</v>
       </c>
       <c r="D242" s="16" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="E242" t="str">
         <f t="shared" si="3"/>
@@ -6811,10 +6505,10 @@
         <v>875</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>524</v>
+        <v>399</v>
       </c>
       <c r="D243" s="16" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E243" t="str">
         <f t="shared" si="3"/>
@@ -6829,10 +6523,10 @@
         <v>877</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>525</v>
+        <v>358</v>
       </c>
       <c r="D244" s="16" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="E244" t="str">
         <f t="shared" si="3"/>
@@ -6847,10 +6541,10 @@
         <v>884</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>526</v>
+        <v>400</v>
       </c>
       <c r="D245" s="16" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E245" t="str">
         <f t="shared" si="3"/>
@@ -6865,10 +6559,10 @@
         <v>885</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>527</v>
+        <v>378</v>
       </c>
       <c r="D246" s="16" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="E246" t="str">
         <f t="shared" si="3"/>
@@ -6883,10 +6577,10 @@
         <v>886</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>439</v>
+        <v>364</v>
       </c>
       <c r="D247" s="16" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E247" t="str">
         <f t="shared" si="3"/>
@@ -6901,10 +6595,10 @@
         <v>891</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>389</v>
+        <v>325</v>
       </c>
       <c r="D248" s="16" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="E248" t="str">
         <f t="shared" si="3"/>
@@ -6919,10 +6613,10 @@
         <v>892</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>528</v>
+        <v>13</v>
       </c>
       <c r="D249" s="16" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="E249" t="str">
         <f t="shared" si="3"/>
@@ -6937,10 +6631,10 @@
         <v>893</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>529</v>
+        <v>13</v>
       </c>
       <c r="D250" s="16" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="E250" t="str">
         <f t="shared" si="3"/>
@@ -6955,10 +6649,10 @@
         <v>895</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>530</v>
+        <v>358</v>
       </c>
       <c r="D251" s="16" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="E251" t="str">
         <f t="shared" si="3"/>
@@ -6973,28 +6667,28 @@
         <v>896</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>531</v>
+        <v>358</v>
       </c>
       <c r="D252" s="16" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="E252" t="str">
         <f t="shared" si="3"/>
         <v>725206896</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1">
+    <row r="253" spans="1:5" ht="16" thickBot="1">
       <c r="A253" t="s">
         <v>41</v>
       </c>
       <c r="B253" s="14">
         <v>897</v>
       </c>
-      <c r="C253" s="24" t="s">
-        <v>532</v>
+      <c r="C253" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="D253" s="19" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="E253" t="str">
         <f t="shared" si="3"/>
